--- a/data/corpus/work_orders_A2.xlsx
+++ b/data/corpus/work_orders_A2.xlsx
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Yukti Refinery – A2_WorkOrders   [SYNTHETIC – SIH DEMO]</t>
+          <t>Example Plant – A2_WorkOrders   [EXAMPLE – prepared by Team UniMinds – NOT MRPL DATA]</t>
         </is>
       </c>
     </row>
